--- a/paper-data/2026-10-15/journal.xlsx
+++ b/paper-data/2026-10-15/journal.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,1270 @@
         <is>
           <t>slippage_bps</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:35:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>244.5922</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.4309</v>
+      </c>
+      <c r="H2" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>gap fade: gap -2.28% (open 243.61 vs prev close 249.29), first 5m bar green; target prev close | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>239.7081</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>249.29</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>244.4700012207031</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:35:33</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>69.801</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.0142</v>
+      </c>
+      <c r="H3" t="n">
+        <v>350</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>gap fade: gap -2.85% (open 68.50 vs prev close 70.51), first 5m bar green; target prev close | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>69.76609802246094</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:41:33</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>70.4747</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.0142</v>
+      </c>
+      <c r="H4" t="n">
+        <v>353.37</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>gap fade: gap -2.85% (open 68.50 vs prev close 70.51), first 5m bar green; target prev close</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>08:35:33</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>69.801</v>
+      </c>
+      <c r="P4" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>70.51000213623047</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:50:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>214.0879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.6348</v>
+      </c>
+      <c r="H5" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VWAP reclaim short EXPERIMENTAL: prior 5m 215.57 &gt; vwap 214.60, close 214.20 &lt; vwap 214.60, vol x1.3 | ctx: v2 px 214.20 vwap 214.60 ema20 218.88; SPY chg -0.44%; SMH chg -3.53%; tod rvol 1.31</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>214.4765</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>213.3107</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>214.1950073242188</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:50:33</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>538.8506</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>303.37</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>VWAP reclaim short EXPERIMENTAL: prior 5m 548.54 &gt; vwap 540.79, close 539.12 &lt; vwap 541.16, vol x1.6 | ctx: v2 px 539.12 vwap 541.16 ema20 561.70; SPY chg -0.44%; SMH chg -3.53%; tod rvol 1.58</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>540.3432</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>535.8653</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>539.1201171875</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:51:33</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>540.6134</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>304.37</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VWAP reclaim short EXPERIMENTAL: prior 5m 548.54 &gt; vwap 540.79, close 539.12 &lt; vwap 541.16, vol x1.6</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.327</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>08:50:33</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>538.8506</v>
+      </c>
+      <c r="P7" t="n">
+        <v>540.3432</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>535.8653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>540.3431884765625</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:55:33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>213.2166</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.6348</v>
+      </c>
+      <c r="H8" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VWAP reclaim short EXPERIMENTAL: prior 5m 215.57 &gt; vwap 214.60, close 214.20 &lt; vwap 214.60, vol x1.3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>08:50:33</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>214.0879</v>
+      </c>
+      <c r="P8" t="n">
+        <v>214.4765</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>213.3107</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>213.1100006103516</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:05:55</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>174.7326</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="H9" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x6.4, close in bottom of range, SPY chg 0.09% | ctx: v2 px 174.82 vwap 175.82 ema20 175.65; SPY chg 0.09%; XLE chg -1.40%; tod rvol 6.42</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>174.9947</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>174.2084</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>174.8200073242188</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:20:55</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>175.0822</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="H10" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x6.4, close in bottom of range, SPY chg 0.09%</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10:05:55</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>174.7326</v>
+      </c>
+      <c r="P10" t="n">
+        <v>174.9947</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>174.2084</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>174.9946962165375</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:35:19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>100.3051</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.4893</v>
+      </c>
+      <c r="H11" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>RVOL spike long EXPERIMENTAL: 5m vol x2.8, close in top of range, SPY chg 0.14% | ctx: v2 px 100.25 vwap 99.42 ema20 99.76; SPY chg 0.14%; XLI chg -0.17%; tod rvol 2.79</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>100.125</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>100.6654</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>100.254997253418</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:50:16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>73.5518</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.1212</v>
+      </c>
+      <c r="H12" t="n">
+        <v>303.12</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>RVOL spike long EXPERIMENTAL: 5m vol x4.1, close in top of range, SPY chg 0.24% | ctx: v2 px 73.51 vwap 70.82 ema20 72.05; SPY chg 0.24%; XLF chg 1.29%; tod rvol 4.09</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>73.205</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>74.2453</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>73.51499938964844</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:09:13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>73.16840000000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.1212</v>
+      </c>
+      <c r="H13" t="n">
+        <v>301.54</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>RVOL spike long EXPERIMENTAL: 5m vol x4.1, close in top of range, SPY chg 0.24%</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.521</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>12:50:16</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>73.5518</v>
+      </c>
+      <c r="P13" t="n">
+        <v>73.205</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>74.2453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>73.20500183105469</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:25:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60.5347</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.9814</v>
+      </c>
+      <c r="H14" t="n">
+        <v>301.55</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x2.8, close in bottom of range, SPY chg -0.03% | ctx: v2 px 60.56 vwap 60.91 ema20 60.73; SPY chg -0.03%; XLE chg -1.58%; tod rvol 2.78</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>60.645</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>60.3141</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>60.56499862670898</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:26:16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>60.6753</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.9814</v>
+      </c>
+      <c r="H15" t="n">
+        <v>302.25</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x2.8, close in bottom of range, SPY chg -0.03%</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>13:25:19</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>60.5347</v>
+      </c>
+      <c r="P15" t="n">
+        <v>60.645</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>60.3141</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>60.64500045776367</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:35:22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100.4498</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.4893</v>
+      </c>
+      <c r="H16" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RVOL spike long EXPERIMENTAL: 5m vol x2.8, close in top of range, SPY chg 0.14%</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>TIME_STOP</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>12:35:19</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>100.3051</v>
+      </c>
+      <c r="P16" t="n">
+        <v>100.125</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>100.6654</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>60</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:55:12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>244.2178</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.4309</v>
+      </c>
+      <c r="H17" t="n">
+        <v>349.45</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>gap fade: gap -2.28% (open 243.61 vs prev close 249.29), first 5m bar green; target prev close</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>EOD_FLATTEN_1455</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>08:35:33</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>244.5922</v>
+      </c>
+      <c r="P17" t="n">
+        <v>239.7081</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>249.29</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="S17" t="n">
+        <v>380</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>244.3399963378906</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -834,13 +2098,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="8">
@@ -863,13 +2133,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="9">
@@ -892,13 +2168,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-2.48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="10">
@@ -987,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +2307,156 @@
         <is>
           <t>rule_changes</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>999.1900000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>653.8200000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>998.47</v>
+      </c>
+      <c r="C3" t="n">
+        <v>653.12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1001.24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>653.12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>999.49</v>
+      </c>
+      <c r="C5" t="n">
+        <v>653.12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>998.14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300.85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>998.17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>651.35</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1073,7 +2505,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:19</t>
+          <t>2026-10-15 15:00:13</t>
         </is>
       </c>
     </row>
@@ -1094,7 +2526,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>1000.8</v>
       </c>
     </row>
     <row r="6">
@@ -1104,7 +2536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>1000.8</v>
       </c>
     </row>
     <row r="7">
@@ -1114,7 +2546,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -1134,7 +2566,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -1144,7 +2576,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1154,7 +2586,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1163,6 +2595,9 @@
           <t>win_rate</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1171,7 +2606,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="14">
